--- a/data/gravel/State Titanium All-Road 2025.xlsx
+++ b/data/gravel/State Titanium All-Road 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E374B70-54E0-8B4E-B07E-88664B7224AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BED07B9B-624B-294A-9EF2-50E131F77BAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="32900" yWindow="-19480" windowWidth="28340" windowHeight="17920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="102">
   <si>
     <t>brand</t>
   </si>
@@ -336,6 +336,9 @@
   </si>
   <si>
     <t>a8:g31</t>
+  </si>
+  <si>
+    <t>https://www.statebicycle.com/cdn/shop/files/State-Bicycle-Co-TitaniumAll-Road-1.jpg?v=1721074433</t>
   </si>
 </sst>
 </file>
@@ -755,6 +758,9 @@
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B6" s="1" t="s">
+        <v>101</v>
+      </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>

--- a/data/gravel/State Titanium All-Road 2025.xlsx
+++ b/data/gravel/State Titanium All-Road 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BED07B9B-624B-294A-9EF2-50E131F77BAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFD8016E-0A78-B541-84D0-FBD12622BE4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32900" yWindow="-19480" windowWidth="28340" windowHeight="17920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7280" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="104">
   <si>
     <t>brand</t>
   </si>
@@ -254,9 +254,6 @@
     <t>trail</t>
   </si>
   <si>
-    <t>usd</t>
-  </si>
-  <si>
     <t>Measurement</t>
   </si>
   <si>
@@ -339,6 +336,15 @@
   </si>
   <si>
     <t>https://www.statebicycle.com/cdn/shop/files/State-Bicycle-Co-TitaniumAll-Road-1.jpg?v=1721074433</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Phoenix, Arizona, USA</t>
+  </si>
+  <si>
+    <t>USD</t>
   </si>
 </sst>
 </file>
@@ -710,7 +716,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L71"/>
+  <dimension ref="A1:L72"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -722,7 +728,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -730,7 +736,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -754,12 +760,12 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
@@ -776,7 +782,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
@@ -793,22 +799,22 @@
         <v>6</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C8" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="E8" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="F8" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="G8" s="6" t="s">
         <v>84</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
@@ -816,7 +822,7 @@
         <v>13</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C9" s="7">
         <v>71</v>
@@ -839,7 +845,7 @@
         <v>12</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C10" s="7">
         <v>437</v>
@@ -862,7 +868,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C11" s="7">
         <v>517</v>
@@ -885,7 +891,7 @@
         <v>18</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C12" s="7">
         <v>45</v>
@@ -908,7 +914,7 @@
         <v>9</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C13" s="7">
         <v>125</v>
@@ -931,7 +937,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C14" s="7">
         <v>70.25</v>
@@ -954,7 +960,7 @@
         <v>17</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C15" s="7">
         <v>367</v>
@@ -977,7 +983,7 @@
         <v>7</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C16" s="7">
         <v>460</v>
@@ -1000,7 +1006,7 @@
         <v>10</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C17" s="7">
         <v>75</v>
@@ -1023,7 +1029,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C18" s="7">
         <v>560</v>
@@ -1046,7 +1052,7 @@
         <v>15</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C19" s="1">
         <f>H19*25.4</f>
@@ -1089,7 +1095,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C20" s="1">
         <v>1021</v>
@@ -1117,7 +1123,7 @@
         <v>23</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C21" s="7">
         <v>1870</v>
@@ -1312,7 +1318,7 @@
         <v>68</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
@@ -1328,7 +1334,7 @@
         <v>31</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
@@ -1399,7 +1405,7 @@
         <v>42</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
@@ -1453,7 +1459,7 @@
         <v>51</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
@@ -1544,7 +1550,15 @@
         <v>65</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>73</v>
+        <v>103</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/State Titanium All-Road 2025.xlsx
+++ b/data/gravel/State Titanium All-Road 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFD8016E-0A78-B541-84D0-FBD12622BE4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D1172B3-7056-234D-A607-87E61007A36B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7280" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="105">
   <si>
     <t>brand</t>
   </si>
@@ -345,6 +345,9 @@
   </si>
   <si>
     <t>USD</t>
+  </si>
+  <si>
+    <t>not spec'd</t>
   </si>
 </sst>
 </file>
@@ -1194,12 +1197,24 @@
       <c r="A28" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
+      <c r="C28" s="4">
+        <v>50</v>
+      </c>
+      <c r="D28" s="4">
+        <v>50</v>
+      </c>
+      <c r="E28" s="4">
+        <v>50</v>
+      </c>
+      <c r="F28" s="4">
+        <v>50</v>
+      </c>
+      <c r="G28" s="4">
+        <v>50</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>104</v>
+      </c>
       <c r="I28" s="4"/>
       <c r="J28" s="4"/>
       <c r="K28" s="4"/>
@@ -1207,6 +1222,21 @@
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>26</v>
+      </c>
+      <c r="C29" s="1">
+        <v>53</v>
+      </c>
+      <c r="D29" s="1">
+        <v>53</v>
+      </c>
+      <c r="E29" s="1">
+        <v>53</v>
+      </c>
+      <c r="F29" s="1">
+        <v>53</v>
+      </c>
+      <c r="G29" s="1">
+        <v>53</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">

--- a/data/gravel/State Titanium All-Road 2025.xlsx
+++ b/data/gravel/State Titanium All-Road 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D1172B3-7056-234D-A607-87E61007A36B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{283AB9B1-7F69-CC4F-82B6-20F62B9CFF24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="111">
   <si>
     <t>brand</t>
   </si>
@@ -348,6 +348,24 @@
   </si>
   <si>
     <t>not spec'd</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -719,7 +737,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L72"/>
+  <dimension ref="A1:L78"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -1432,162 +1450,192 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>43</v>
+        <v>106</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B50" s="1">
-        <v>27.2</v>
+        <v>107</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>71</v>
+        <v>108</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>46</v>
+        <v>109</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>47</v>
+        <v>110</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>50</v>
+        <v>44</v>
+      </c>
+      <c r="B56" s="1">
+        <v>27.2</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>71</v>
+        <v>48</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B61" s="1">
-        <v>2</v>
+        <v>49</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B62" s="1">
-        <v>1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>60</v>
+        <v>54</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>61</v>
+        <v>55</v>
+      </c>
+      <c r="B67" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B68" s="1">
-        <v>1299</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B69" s="1">
-        <v>2299</v>
+        <v>57</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>103</v>
+        <v>59</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B74" s="1">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B75" s="1">
+        <v>2299</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B72" s="1" t="s">
+      <c r="B78" s="1" t="s">
         <v>102</v>
       </c>
     </row>
